--- a/selfcheck-gpt/result.xlsx
+++ b/selfcheck-gpt/result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\ai-bachelor\selfcheck-gpt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A43326-8F13-472C-A148-03D749BB8E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EC1371-030A-453E-8BA2-DF5D517562AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{A1709077-84EA-4464-8910-9ADD31DE5478}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="76">
   <si>
     <t>Method</t>
   </si>
@@ -274,6 +274,27 @@
   <si>
     <t>w/ Prompt 
 gpt-3.5-turbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.87	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.40	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.53	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.94	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w/ Prompt - test
+Solar Pro	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w/ Prompt - test
+Llama-3.2-1B	
+</t>
   </si>
 </sst>
 </file>
@@ -339,7 +360,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -386,7 +407,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -721,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1062B39-17AA-4172-A9CB-D35D14BD091F}">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.6328125" style="2" customWidth="1"/>
@@ -1287,7 +1307,7 @@
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="16" t="s">
+      <c r="G31" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1495,10 +1515,11 @@
       <c r="A44" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="3">
         <v>89.05</v>
       </c>
-      <c r="D44">
+      <c r="C44" s="3"/>
+      <c r="D44" s="3">
         <v>63.06</v>
       </c>
     </row>
@@ -1506,10 +1527,11 @@
       <c r="A45" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="3">
         <v>91.91</v>
       </c>
-      <c r="D45">
+      <c r="C45" s="3"/>
+      <c r="D45" s="3">
         <v>64.34</v>
       </c>
     </row>
@@ -1517,10 +1539,11 @@
       <c r="A46" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="3">
         <v>91.31</v>
       </c>
-      <c r="D46">
+      <c r="C46" s="3"/>
+      <c r="D46" s="3">
         <v>62.76</v>
       </c>
     </row>
@@ -1528,11 +1551,40 @@
       <c r="A47" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="3">
         <v>93.42</v>
       </c>
-      <c r="D47">
+      <c r="C47" s="3"/>
+      <c r="D47" s="3">
         <v>67.09</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D48" s="4">
+        <v>19.61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A49" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="4">
+        <v>69.349999999999994</v>
       </c>
     </row>
   </sheetData>
